--- a/matrixify/divine-bulk-import.xlsx
+++ b/matrixify/divine-bulk-import.xlsx
@@ -6562,7 +6562,7 @@
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>Rule: Column</t>
+          <t>Rule: Product Column</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
@@ -6625,12 +6625,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>TAG</t>
+          <t>Tag</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>EQUALS</t>
+          <t>is equal to</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -6688,12 +6688,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>TAG</t>
+          <t>Tag</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>EQUALS</t>
+          <t>is equal to</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -6751,12 +6751,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>TAG</t>
+          <t>Tag</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>EQUALS</t>
+          <t>is equal to</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -6814,12 +6814,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>TAG</t>
+          <t>Tag</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>EQUALS</t>
+          <t>is equal to</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -6877,12 +6877,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>TAG</t>
+          <t>Tag</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>EQUALS</t>
+          <t>is equal to</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -6936,12 +6936,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>TAG</t>
+          <t>Tag</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>EQUALS</t>
+          <t>is equal to</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -6991,12 +6991,12 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>TAG</t>
+          <t>Tag</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>EQUALS</t>
+          <t>is equal to</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -7046,12 +7046,12 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>TAG</t>
+          <t>Tag</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>EQUALS</t>
+          <t>is equal to</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -7101,12 +7101,12 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>TAG</t>
+          <t>Tag</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>EQUALS</t>
+          <t>is equal to</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -7156,12 +7156,12 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>TAG</t>
+          <t>Tag</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>EQUALS</t>
+          <t>is equal to</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -7211,12 +7211,12 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>TAG</t>
+          <t>Tag</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>EQUALS</t>
+          <t>is equal to</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -7266,12 +7266,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>TAG</t>
+          <t>Tag</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>EQUALS</t>
+          <t>is equal to</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -7325,12 +7325,12 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>TAG</t>
+          <t>Tag</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>EQUALS</t>
+          <t>is equal to</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -7388,12 +7388,12 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>TAG</t>
+          <t>Tag</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>EQUALS</t>
+          <t>is equal to</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -7451,12 +7451,12 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>TAG</t>
+          <t>Tag</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>EQUALS</t>
+          <t>is equal to</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -7514,12 +7514,12 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>TAG</t>
+          <t>Tag</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>EQUALS</t>
+          <t>is equal to</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -7577,12 +7577,12 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>TAG</t>
+          <t>Tag</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>EQUALS</t>
+          <t>is equal to</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">

--- a/matrixify/divine-bulk-import.xlsx
+++ b/matrixify/divine-bulk-import.xlsx
@@ -6630,7 +6630,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>is equal to</t>
+          <t>Equals</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -6693,7 +6693,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>is equal to</t>
+          <t>Equals</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -6756,7 +6756,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>is equal to</t>
+          <t>Equals</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -6819,7 +6819,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>is equal to</t>
+          <t>Equals</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -6882,7 +6882,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>is equal to</t>
+          <t>Equals</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -6941,7 +6941,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>is equal to</t>
+          <t>Equals</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -6996,7 +6996,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>is equal to</t>
+          <t>Equals</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -7051,7 +7051,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>is equal to</t>
+          <t>Equals</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -7106,7 +7106,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>is equal to</t>
+          <t>Equals</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -7161,7 +7161,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>is equal to</t>
+          <t>Equals</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -7216,7 +7216,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>is equal to</t>
+          <t>Equals</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -7271,7 +7271,7 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>is equal to</t>
+          <t>Equals</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -7330,7 +7330,7 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>is equal to</t>
+          <t>Equals</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -7393,7 +7393,7 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>is equal to</t>
+          <t>Equals</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -7456,7 +7456,7 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>is equal to</t>
+          <t>Equals</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -7519,7 +7519,7 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>is equal to</t>
+          <t>Equals</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -7582,7 +7582,7 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>is equal to</t>
+          <t>Equals</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">

--- a/matrixify/divine-bulk-import.xlsx
+++ b/matrixify/divine-bulk-import.xlsx
@@ -6557,7 +6557,7 @@
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>Disjunctive</t>
+          <t>Must Match</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
@@ -6609,18 +6609,18 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>best-selling</t>
+          <t>Best Selling</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>True</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>all conditions</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -6672,18 +6672,18 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>best-selling</t>
+          <t>Best Selling</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>True</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>all conditions</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -6735,18 +6735,18 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>best-selling</t>
+          <t>Best Selling</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>True</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>all conditions</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -6798,18 +6798,18 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>best-selling</t>
+          <t>Best Selling</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>True</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>all conditions</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -6861,18 +6861,18 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>best-selling</t>
+          <t>Best Selling</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>True</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>all conditions</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -6920,18 +6920,18 @@
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>best-selling</t>
+          <t>Best Selling</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>True</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>all conditions</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -6975,18 +6975,18 @@
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>best-selling</t>
+          <t>Best Selling</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>True</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>all conditions</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -7030,18 +7030,18 @@
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>best-selling</t>
+          <t>Best Selling</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>True</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>all conditions</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -7085,18 +7085,18 @@
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>best-selling</t>
+          <t>Best Selling</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>True</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>all conditions</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -7140,18 +7140,18 @@
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>best-selling</t>
+          <t>Best Selling</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>True</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>all conditions</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -7195,18 +7195,18 @@
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>best-selling</t>
+          <t>Best Selling</t>
         </is>
       </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>True</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>all conditions</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -7250,18 +7250,18 @@
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>best-selling</t>
+          <t>Best Selling</t>
         </is>
       </c>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>True</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>all conditions</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -7309,18 +7309,18 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>best-selling</t>
+          <t>Best Selling</t>
         </is>
       </c>
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>True</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>all conditions</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -7372,18 +7372,18 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>best-selling</t>
+          <t>Best Selling</t>
         </is>
       </c>
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>True</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>all conditions</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -7435,18 +7435,18 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>best-selling</t>
+          <t>Best Selling</t>
         </is>
       </c>
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>True</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>all conditions</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -7498,18 +7498,18 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>best-selling</t>
+          <t>Best Selling</t>
         </is>
       </c>
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>True</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>all conditions</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -7561,18 +7561,18 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>best-selling</t>
+          <t>Best Selling</t>
         </is>
       </c>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>True</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>all conditions</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">

--- a/matrixify/divine-bulk-import.xlsx
+++ b/matrixify/divine-bulk-import.xlsx
@@ -1349,7 +1349,11 @@
         </is>
       </c>
       <c r="X11" t="inlineStr"/>
-      <c r="Y11" t="inlineStr"/>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
       <c r="Z11" t="inlineStr">
         <is>
           <t>shopify</t>
@@ -1946,7 +1950,11 @@
         </is>
       </c>
       <c r="X18" t="inlineStr"/>
-      <c r="Y18" t="inlineStr"/>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
       <c r="Z18" t="inlineStr">
         <is>
           <t>shopify</t>
@@ -2456,7 +2464,11 @@
         </is>
       </c>
       <c r="X24" t="inlineStr"/>
-      <c r="Y24" t="inlineStr"/>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
       <c r="Z24" t="inlineStr">
         <is>
           <t>shopify</t>
@@ -5024,7 +5036,11 @@
         </is>
       </c>
       <c r="X60" t="inlineStr"/>
-      <c r="Y60" t="inlineStr"/>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
       <c r="Z60" t="inlineStr">
         <is>
           <t>shopify</t>
@@ -5652,7 +5668,11 @@
         </is>
       </c>
       <c r="X68" t="inlineStr"/>
-      <c r="Y68" t="inlineStr"/>
+      <c r="Y68" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
       <c r="Z68" t="inlineStr">
         <is>
           <t>shopify</t>
@@ -5929,7 +5949,11 @@
         </is>
       </c>
       <c r="X71" t="inlineStr"/>
-      <c r="Y71" t="inlineStr"/>
+      <c r="Y71" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
       <c r="Z71" t="inlineStr">
         <is>
           <t>shopify</t>
@@ -6056,7 +6080,11 @@
         </is>
       </c>
       <c r="X72" t="inlineStr"/>
-      <c r="Y72" t="inlineStr"/>
+      <c r="Y72" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
       <c r="Z72" t="inlineStr">
         <is>
           <t>shopify</t>
@@ -6183,7 +6211,11 @@
         </is>
       </c>
       <c r="X73" t="inlineStr"/>
-      <c r="Y73" t="inlineStr"/>
+      <c r="Y73" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
       <c r="Z73" t="inlineStr">
         <is>
           <t>shopify</t>
@@ -7612,7 +7644,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H18"/>
+  <dimension ref="A1:H28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8343,6 +8375,386 @@
       </c>
       <c r="H18" t="inlineStr"/>
     </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>footer-by-function</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>MERGE</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Footer: Shop by Function</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Immunity</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Collection</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>immunity</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>footer-by-function</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>MERGE</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Footer: Shop by Function</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Wind Down</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Collection</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>wind-down</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>footer-by-function</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>MERGE</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Footer: Shop by Function</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Gut Reset</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Collection</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>gut-reset</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>footer-by-function</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>MERGE</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Footer: Shop by Function</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Focus &amp; Energy</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Collection</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>focus-and-energy</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>footer-by-function</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>MERGE</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Footer: Shop by Function</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Detox</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Collection</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>detox</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>footer-by-category</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>MERGE</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Footer: Shop</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>All Teas</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Collection</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>all-teas</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>footer-by-category</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>MERGE</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Footer: Shop</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Powders</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Collection</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>all-powders</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>footer-by-category</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>MERGE</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Footer: Shop</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Spices &amp; Botanicals</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Collection</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>spices-botanicals</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>footer-by-category</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>MERGE</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Footer: Shop</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>All Organic</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Collection</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>all-organic</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>footer-by-category</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>MERGE</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Footer: Shop</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Founders' Favourites</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Collection</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>founders-favourites</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/matrixify/divine-bulk-import.xlsx
+++ b/matrixify/divine-bulk-import.xlsx
@@ -6936,7 +6936,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>green-tea</t>
+          <t>green-teas</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -6991,7 +6991,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>black-tea</t>
+          <t>black-teas</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -7211,7 +7211,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>iced-tea</t>
+          <t>iced-teas</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -7644,7 +7644,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H28"/>
+  <dimension ref="A1:J28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7670,22 +7670,32 @@
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>Menu Item: Type</t>
+          <t>Menu Item: Command</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>Menu Item: Resource</t>
+          <t>Menu Item: Resource Type</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
+          <t>Menu Item: Resource Handle</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Menu Item: URL</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>Menu Item: Parent Title</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
           <t>Menu Item: Position</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>Menu Item: Parent</t>
         </is>
       </c>
     </row>
@@ -7712,16 +7722,26 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Link</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr">
+          <t>MERGE</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>HTTP</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>/collections</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -7746,22 +7766,32 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Collection</t>
+          <t>MERGE</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
+          <t>COLLECTION</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
           <t>immunity</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="H3" t="inlineStr">
         <is>
+          <t>/collections/immunity</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
           <t>Shop by Function</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -7783,27 +7813,37 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Wind down</t>
+          <t>Wind Down</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Collection</t>
+          <t>MERGE</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
+          <t>COLLECTION</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
           <t>wind-down</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="H4" t="inlineStr">
         <is>
+          <t>/collections/wind-down</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
           <t>Shop by Function</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -7830,22 +7870,32 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Collection</t>
+          <t>MERGE</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
+          <t>COLLECTION</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
           <t>gut-reset</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="H5" t="inlineStr">
         <is>
+          <t>/collections/gut-reset</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
           <t>Shop by Function</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>3</t>
         </is>
       </c>
     </row>
@@ -7867,27 +7917,37 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Focus and Energy</t>
+          <t>Focus &amp; Energy</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Collection</t>
+          <t>MERGE</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
+          <t>COLLECTION</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
           <t>focus-and-energy</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="H6" t="inlineStr">
         <is>
+          <t>/collections/focus-and-energy</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
           <t>Shop by Function</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>4</t>
         </is>
       </c>
     </row>
@@ -7914,22 +7974,32 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Collection</t>
+          <t>MERGE</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
+          <t>COLLECTION</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
           <t>detox</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="H7" t="inlineStr">
         <is>
+          <t>/collections/detox</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
           <t>Shop by Function</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>5</t>
         </is>
       </c>
     </row>
@@ -7956,16 +8026,26 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Link</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr"/>
+          <t>MERGE</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>HTTP</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>/collections</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -7990,22 +8070,32 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Collection</t>
+          <t>MERGE</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>green-tea</t>
+          <t>COLLECTION</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>green-teas</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
+          <t>/collections/green-teas</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
           <t>Shop by Type</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -8032,22 +8122,32 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Collection</t>
+          <t>MERGE</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>black-tea</t>
+          <t>COLLECTION</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>black-teas</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
+          <t>/collections/black-teas</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
           <t>Shop by Type</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -8074,22 +8174,32 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Collection</t>
+          <t>MERGE</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
+          <t>COLLECTION</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
           <t>herbal-tea</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
       <c r="H11" t="inlineStr">
         <is>
+          <t>/collections/herbal-tea</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
           <t>Shop by Type</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>3</t>
         </is>
       </c>
     </row>
@@ -8116,22 +8226,32 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Collection</t>
+          <t>MERGE</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
+          <t>COLLECTION</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
           <t>chai</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
       <c r="H12" t="inlineStr">
         <is>
+          <t>/collections/chai</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
           <t>Shop by Type</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>4</t>
         </is>
       </c>
     </row>
@@ -8158,22 +8278,32 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Collection</t>
+          <t>MERGE</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
+          <t>COLLECTION</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
           <t>matcha</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
       <c r="H13" t="inlineStr">
         <is>
+          <t>/collections/matcha</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
           <t>Shop by Type</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>5</t>
         </is>
       </c>
     </row>
@@ -8200,22 +8330,32 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Collection</t>
+          <t>MERGE</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>iced-tea</t>
+          <t>COLLECTION</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>iced-teas</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
+          <t>/collections/iced-teas</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
           <t>Shop by Type</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>6</t>
         </is>
       </c>
     </row>
@@ -8242,22 +8382,32 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Collection</t>
+          <t>MERGE</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
+          <t>COLLECTION</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
           <t>boba-boba</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
       <c r="H15" t="inlineStr">
         <is>
+          <t>/collections/boba-boba</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
           <t>Shop by Type</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>7</t>
         </is>
       </c>
     </row>
@@ -8284,20 +8434,30 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Collection</t>
+          <t>MERGE</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
+          <t>COLLECTION</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
           <t>all-powders</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr"/>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>/collections/all-powders</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -8322,20 +8482,30 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Collection</t>
+          <t>MERGE</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
+          <t>COLLECTION</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
           <t>spices-botanicals</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr"/>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>/collections/spices-botanicals</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -8360,20 +8530,30 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Collection</t>
+          <t>MERGE</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
+          <t>COLLECTION</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
           <t>founders-favourites</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr"/>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>/collections/founders-favourites</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -8398,20 +8578,30 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Collection</t>
+          <t>MERGE</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
+          <t>COLLECTION</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
           <t>immunity</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr">
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>/collections/immunity</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -8436,20 +8626,30 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Collection</t>
+          <t>MERGE</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
+          <t>COLLECTION</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
           <t>wind-down</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr">
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>/collections/wind-down</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -8474,20 +8674,30 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Collection</t>
+          <t>MERGE</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
+          <t>COLLECTION</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
           <t>gut-reset</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr">
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>/collections/gut-reset</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -8512,20 +8722,30 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Collection</t>
+          <t>MERGE</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
+          <t>COLLECTION</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
           <t>focus-and-energy</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr">
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>/collections/focus-and-energy</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -8550,20 +8770,30 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Collection</t>
+          <t>MERGE</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
+          <t>COLLECTION</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
           <t>detox</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr">
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>/collections/detox</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -8588,20 +8818,30 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Collection</t>
+          <t>MERGE</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
+          <t>COLLECTION</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
           <t>all-teas</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr">
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>/collections/all-teas</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -8626,20 +8866,30 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Collection</t>
+          <t>MERGE</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
+          <t>COLLECTION</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
           <t>all-powders</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr">
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>/collections/all-powders</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -8664,20 +8914,30 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Collection</t>
+          <t>MERGE</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
+          <t>COLLECTION</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
           <t>spices-botanicals</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr">
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>/collections/spices-botanicals</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -8702,20 +8962,30 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Collection</t>
+          <t>MERGE</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
+          <t>COLLECTION</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
           <t>all-organic</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr">
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>/collections/all-organic</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -8740,20 +9010,30 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Collection</t>
+          <t>MERGE</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
+          <t>COLLECTION</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
           <t>founders-favourites</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr">
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>/collections/founders-favourites</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/matrixify/divine-bulk-import.xlsx
+++ b/matrixify/divine-bulk-import.xlsx
@@ -1087,15 +1087,31 @@
           <t>Coffee Cherry Powder</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr"/>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Category_Powder, Format_Powder</t>
+        </is>
+      </c>
       <c r="E8" t="inlineStr">
         <is>
           <t>MERGE</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>All Powders</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
@@ -1154,15 +1170,31 @@
           <t>Conventional Jasmine Flowers Botanicals</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr"/>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Category_Spices_Botanicals, Format_Botanical</t>
+        </is>
+      </c>
       <c r="E9" t="inlineStr">
         <is>
           <t>MERGE</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Spices &amp; Botanicals</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
@@ -1217,15 +1249,31 @@
           <t>Conventional Rose Petals Botanicals</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr"/>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Category_Spices_Botanicals, Format_Botanical</t>
+        </is>
+      </c>
       <c r="E10" t="inlineStr">
         <is>
           <t>MERGE</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Spices &amp; Botanicals</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
@@ -1272,7 +1320,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>MERGE</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1873,7 +1921,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>MERGE</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -2403,7 +2451,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>MERGE</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -2980,15 +3028,31 @@
           <t>Organic Ashwagandha Root Powder</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr"/>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Category_Powder, Format_Powder, Organic</t>
+        </is>
+      </c>
       <c r="E31" t="inlineStr">
         <is>
           <t>MERGE</t>
         </is>
       </c>
-      <c r="F31" t="inlineStr"/>
-      <c r="G31" t="inlineStr"/>
-      <c r="H31" t="inlineStr"/>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>All Organic; All Powders</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
       <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
@@ -3134,15 +3198,31 @@
           <t>Organic Blueberry Powder</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr"/>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Category_Powder, Format_Powder, Organic</t>
+        </is>
+      </c>
       <c r="E33" t="inlineStr">
         <is>
           <t>MERGE</t>
         </is>
       </c>
-      <c r="F33" t="inlineStr"/>
-      <c r="G33" t="inlineStr"/>
-      <c r="H33" t="inlineStr"/>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>All Organic; All Powders</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
       <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
@@ -3201,15 +3281,31 @@
           <t>Organic Calendula Petals Botanicals</t>
         </is>
       </c>
-      <c r="D34" t="inlineStr"/>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Category_Spices_Botanicals, Format_Botanical, Organic</t>
+        </is>
+      </c>
       <c r="E34" t="inlineStr">
         <is>
           <t>MERGE</t>
         </is>
       </c>
-      <c r="F34" t="inlineStr"/>
-      <c r="G34" t="inlineStr"/>
-      <c r="H34" t="inlineStr"/>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>All Organic; Spices &amp; Botanicals</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
       <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
@@ -3264,15 +3360,31 @@
           <t>Organic Chamomile Flowers Botanicals</t>
         </is>
       </c>
-      <c r="D35" t="inlineStr"/>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Category_Spices_Botanicals, Format_Botanical, Organic</t>
+        </is>
+      </c>
       <c r="E35" t="inlineStr">
         <is>
           <t>MERGE</t>
         </is>
       </c>
-      <c r="F35" t="inlineStr"/>
-      <c r="G35" t="inlineStr"/>
-      <c r="H35" t="inlineStr"/>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>All Organic; Spices &amp; Botanicals</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
       <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
@@ -3327,15 +3439,31 @@
           <t>Organic Coconut Milk Powder</t>
         </is>
       </c>
-      <c r="D36" t="inlineStr"/>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Category_Powder, Format_Powder, Organic</t>
+        </is>
+      </c>
       <c r="E36" t="inlineStr">
         <is>
           <t>MERGE</t>
         </is>
       </c>
-      <c r="F36" t="inlineStr"/>
-      <c r="G36" t="inlineStr"/>
-      <c r="H36" t="inlineStr"/>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>All Organic; All Powders</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
       <c r="I36" t="inlineStr"/>
       <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
@@ -3394,15 +3522,31 @@
           <t>Organic Cordyceps Powder</t>
         </is>
       </c>
-      <c r="D37" t="inlineStr"/>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Category_Powder, Format_Powder, Organic</t>
+        </is>
+      </c>
       <c r="E37" t="inlineStr">
         <is>
           <t>MERGE</t>
         </is>
       </c>
-      <c r="F37" t="inlineStr"/>
-      <c r="G37" t="inlineStr"/>
-      <c r="H37" t="inlineStr"/>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>All Organic; All Powders</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
       <c r="I37" t="inlineStr"/>
       <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
@@ -3461,15 +3605,31 @@
           <t>Organic Date Powder</t>
         </is>
       </c>
-      <c r="D38" t="inlineStr"/>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Category_Powder, Format_Powder, Organic</t>
+        </is>
+      </c>
       <c r="E38" t="inlineStr">
         <is>
           <t>MERGE</t>
         </is>
       </c>
-      <c r="F38" t="inlineStr"/>
-      <c r="G38" t="inlineStr"/>
-      <c r="H38" t="inlineStr"/>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>All Organic; All Powders</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
       <c r="I38" t="inlineStr"/>
       <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
@@ -3528,15 +3688,31 @@
           <t>Organic Elderberries Botanicals</t>
         </is>
       </c>
-      <c r="D39" t="inlineStr"/>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Category_Spices_Botanicals, Format_Botanical, Organic</t>
+        </is>
+      </c>
       <c r="E39" t="inlineStr">
         <is>
           <t>MERGE</t>
         </is>
       </c>
-      <c r="F39" t="inlineStr"/>
-      <c r="G39" t="inlineStr"/>
-      <c r="H39" t="inlineStr"/>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>All Organic; Spices &amp; Botanicals</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
       <c r="I39" t="inlineStr"/>
       <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
@@ -3591,15 +3767,31 @@
           <t>Organic Green Rooibos Botanicals</t>
         </is>
       </c>
-      <c r="D40" t="inlineStr"/>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Category_Spices_Botanicals, Format_Botanical, Organic</t>
+        </is>
+      </c>
       <c r="E40" t="inlineStr">
         <is>
           <t>MERGE</t>
         </is>
       </c>
-      <c r="F40" t="inlineStr"/>
-      <c r="G40" t="inlineStr"/>
-      <c r="H40" t="inlineStr"/>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>All Organic; Spices &amp; Botanicals</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
       <c r="I40" t="inlineStr"/>
       <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr"/>
@@ -3721,15 +3913,31 @@
           <t>Organic Hibiscus Botanicals</t>
         </is>
       </c>
-      <c r="D42" t="inlineStr"/>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Category_Spices_Botanicals, Format_Botanical, Organic</t>
+        </is>
+      </c>
       <c r="E42" t="inlineStr">
         <is>
           <t>MERGE</t>
         </is>
       </c>
-      <c r="F42" t="inlineStr"/>
-      <c r="G42" t="inlineStr"/>
-      <c r="H42" t="inlineStr"/>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>All Organic; Spices &amp; Botanicals</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
       <c r="I42" t="inlineStr"/>
       <c r="J42" t="inlineStr"/>
       <c r="K42" t="inlineStr"/>
@@ -3855,15 +4063,31 @@
           <t>Organic Lemongrass Botanicals</t>
         </is>
       </c>
-      <c r="D44" t="inlineStr"/>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Category_Spices_Botanicals, Format_Botanical, Organic</t>
+        </is>
+      </c>
       <c r="E44" t="inlineStr">
         <is>
           <t>MERGE</t>
         </is>
       </c>
-      <c r="F44" t="inlineStr"/>
-      <c r="G44" t="inlineStr"/>
-      <c r="H44" t="inlineStr"/>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>All Organic; Spices &amp; Botanicals</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
       <c r="I44" t="inlineStr"/>
       <c r="J44" t="inlineStr"/>
       <c r="K44" t="inlineStr"/>
@@ -3918,15 +4142,31 @@
           <t>Organic Licorice Spice</t>
         </is>
       </c>
-      <c r="D45" t="inlineStr"/>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Category_Spices_Botanicals, Format_Spice, Organic</t>
+        </is>
+      </c>
       <c r="E45" t="inlineStr">
         <is>
           <t>MERGE</t>
         </is>
       </c>
-      <c r="F45" t="inlineStr"/>
-      <c r="G45" t="inlineStr"/>
-      <c r="H45" t="inlineStr"/>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>All Organic; Spices &amp; Botanicals</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
       <c r="I45" t="inlineStr"/>
       <c r="J45" t="inlineStr"/>
       <c r="K45" t="inlineStr"/>
@@ -3981,15 +4221,31 @@
           <t>Organic Lion's Mane Powder</t>
         </is>
       </c>
-      <c r="D46" t="inlineStr"/>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Category_Powder, Format_Powder, Organic</t>
+        </is>
+      </c>
       <c r="E46" t="inlineStr">
         <is>
           <t>MERGE</t>
         </is>
       </c>
-      <c r="F46" t="inlineStr"/>
-      <c r="G46" t="inlineStr"/>
-      <c r="H46" t="inlineStr"/>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>All Organic; All Powders</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
       <c r="I46" t="inlineStr"/>
       <c r="J46" t="inlineStr"/>
       <c r="K46" t="inlineStr"/>
@@ -4048,15 +4304,31 @@
           <t>Organic Molasses Powder</t>
         </is>
       </c>
-      <c r="D47" t="inlineStr"/>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Category_Powder, Format_Powder, Organic</t>
+        </is>
+      </c>
       <c r="E47" t="inlineStr">
         <is>
           <t>MERGE</t>
         </is>
       </c>
-      <c r="F47" t="inlineStr"/>
-      <c r="G47" t="inlineStr"/>
-      <c r="H47" t="inlineStr"/>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>All Organic; All Powders</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
       <c r="I47" t="inlineStr"/>
       <c r="J47" t="inlineStr"/>
       <c r="K47" t="inlineStr"/>
@@ -4115,15 +4387,31 @@
           <t>Organic Reishi Mushroom Powder</t>
         </is>
       </c>
-      <c r="D48" t="inlineStr"/>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Category_Powder, Format_Powder, Organic</t>
+        </is>
+      </c>
       <c r="E48" t="inlineStr">
         <is>
           <t>MERGE</t>
         </is>
       </c>
-      <c r="F48" t="inlineStr"/>
-      <c r="G48" t="inlineStr"/>
-      <c r="H48" t="inlineStr"/>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>All Organic; All Powders</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
       <c r="I48" t="inlineStr"/>
       <c r="J48" t="inlineStr"/>
       <c r="K48" t="inlineStr"/>
@@ -4182,15 +4470,31 @@
           <t>Organic Rhodiola Root Powder</t>
         </is>
       </c>
-      <c r="D49" t="inlineStr"/>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Category_Powder, Format_Powder, Organic</t>
+        </is>
+      </c>
       <c r="E49" t="inlineStr">
         <is>
           <t>MERGE</t>
         </is>
       </c>
-      <c r="F49" t="inlineStr"/>
-      <c r="G49" t="inlineStr"/>
-      <c r="H49" t="inlineStr"/>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>All Organic; All Powders</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
       <c r="I49" t="inlineStr"/>
       <c r="J49" t="inlineStr"/>
       <c r="K49" t="inlineStr"/>
@@ -4249,15 +4553,31 @@
           <t>Organic Rose Petals Powder</t>
         </is>
       </c>
-      <c r="D50" t="inlineStr"/>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Category_Powder, Format_Powder, Organic</t>
+        </is>
+      </c>
       <c r="E50" t="inlineStr">
         <is>
           <t>MERGE</t>
         </is>
       </c>
-      <c r="F50" t="inlineStr"/>
-      <c r="G50" t="inlineStr"/>
-      <c r="H50" t="inlineStr"/>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>All Organic; All Powders</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
       <c r="I50" t="inlineStr"/>
       <c r="J50" t="inlineStr"/>
       <c r="K50" t="inlineStr"/>
@@ -4316,15 +4636,31 @@
           <t>Organic Rosehips Botanicals</t>
         </is>
       </c>
-      <c r="D51" t="inlineStr"/>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Category_Spices_Botanicals, Format_Botanical, Organic</t>
+        </is>
+      </c>
       <c r="E51" t="inlineStr">
         <is>
           <t>MERGE</t>
         </is>
       </c>
-      <c r="F51" t="inlineStr"/>
-      <c r="G51" t="inlineStr"/>
-      <c r="H51" t="inlineStr"/>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>All Organic; Spices &amp; Botanicals</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
       <c r="I51" t="inlineStr"/>
       <c r="J51" t="inlineStr"/>
       <c r="K51" t="inlineStr"/>
@@ -4379,15 +4715,31 @@
           <t>Organic Star Anise Spice</t>
         </is>
       </c>
-      <c r="D52" t="inlineStr"/>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Category_Spices_Botanicals, Format_Spice, Organic</t>
+        </is>
+      </c>
       <c r="E52" t="inlineStr">
         <is>
           <t>MERGE</t>
         </is>
       </c>
-      <c r="F52" t="inlineStr"/>
-      <c r="G52" t="inlineStr"/>
-      <c r="H52" t="inlineStr"/>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>All Organic; Spices &amp; Botanicals</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
       <c r="I52" t="inlineStr"/>
       <c r="J52" t="inlineStr"/>
       <c r="K52" t="inlineStr"/>
@@ -4442,15 +4794,31 @@
           <t>Organic Supreme Matcha Green Tea Powder</t>
         </is>
       </c>
-      <c r="D53" t="inlineStr"/>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Category_Powder, Format_Powder, Organic</t>
+        </is>
+      </c>
       <c r="E53" t="inlineStr">
         <is>
           <t>MERGE</t>
         </is>
       </c>
-      <c r="F53" t="inlineStr"/>
-      <c r="G53" t="inlineStr"/>
-      <c r="H53" t="inlineStr"/>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>All Organic; All Powders</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
       <c r="I53" t="inlineStr"/>
       <c r="J53" t="inlineStr"/>
       <c r="K53" t="inlineStr"/>
@@ -4509,15 +4877,31 @@
           <t>Organic Taro Powder</t>
         </is>
       </c>
-      <c r="D54" t="inlineStr"/>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Category_Powder, Format_Powder, Organic</t>
+        </is>
+      </c>
       <c r="E54" t="inlineStr">
         <is>
           <t>MERGE</t>
         </is>
       </c>
-      <c r="F54" t="inlineStr"/>
-      <c r="G54" t="inlineStr"/>
-      <c r="H54" t="inlineStr"/>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>All Organic; All Powders</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
       <c r="I54" t="inlineStr"/>
       <c r="J54" t="inlineStr"/>
       <c r="K54" t="inlineStr"/>
@@ -4576,15 +4960,31 @@
           <t>Organic Tart Cherries Powder</t>
         </is>
       </c>
-      <c r="D55" t="inlineStr"/>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Category_Powder, Format_Powder, Organic</t>
+        </is>
+      </c>
       <c r="E55" t="inlineStr">
         <is>
           <t>MERGE</t>
         </is>
       </c>
-      <c r="F55" t="inlineStr"/>
-      <c r="G55" t="inlineStr"/>
-      <c r="H55" t="inlineStr"/>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>All Organic; All Powders</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
       <c r="I55" t="inlineStr"/>
       <c r="J55" t="inlineStr"/>
       <c r="K55" t="inlineStr"/>
@@ -4730,15 +5130,31 @@
           <t>Organic Valerian Root Botanicals</t>
         </is>
       </c>
-      <c r="D57" t="inlineStr"/>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Category_Spices_Botanicals, Format_Botanical, Organic</t>
+        </is>
+      </c>
       <c r="E57" t="inlineStr">
         <is>
           <t>MERGE</t>
         </is>
       </c>
-      <c r="F57" t="inlineStr"/>
-      <c r="G57" t="inlineStr"/>
-      <c r="H57" t="inlineStr"/>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>All Organic; Spices &amp; Botanicals</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
       <c r="I57" t="inlineStr"/>
       <c r="J57" t="inlineStr"/>
       <c r="K57" t="inlineStr"/>
@@ -4955,7 +5371,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>MERGE</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -5607,7 +6023,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>MERGE</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -5872,7 +6288,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>MERGE</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -5999,7 +6415,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>MERGE</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -6130,7 +6546,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>MERGE</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -7211,7 +7627,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>iced-teas</t>
+          <t>iced-tea-collection</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -8340,12 +8756,12 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>iced-teas</t>
+          <t>iced-tea-collection</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>/collections/iced-teas</t>
+          <t>/collections/iced-tea-collection</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
